--- a/courses/2/networks/dist/Учебный_план_Компьютерные_сети.xlsx
+++ b/courses/2/networks/dist/Учебный_план_Компьютерные_сети.xlsx
@@ -195,16 +195,16 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Компьютерные сети: назначение»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Сеть связывает устройства, чтобы они делили ресурсы и обменивались данными. Разбираются виды сетей, топологии и цена общей среды.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Компьютерные сети: назначение</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1">
+          <t xml:space="preserve">узел, топология, локальная сеть, ресурс, среда передачи</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
@@ -225,12 +225,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Настройка сети в VirtualBox»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Две виртуальные машины соединяются в сеть внутри VirtualBox: режим адаптера, адреса, проверка связи. Сдаётся отчёт со схемой и выводом команд проверки.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Настройка сети в VirtualBox</t>
+          <t xml:space="preserve">виртуальная машина, адаптер, NAT, ping, хост</t>
         </is>
       </c>
     </row>
@@ -255,16 +255,16 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Модель OSI»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Семь уровней OSI делят задачу передачи на слои: от кабеля до приложения. Каждый уровень добавляет свой заголовок и работает с данными по-своему.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Модель OSI</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1">
+          <t xml:space="preserve">уровень, инкапсуляция, заголовок, прикладной уровень, канальный уровень</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
@@ -285,12 +285,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «IP-адресация и маски»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Расчёт адресов для небольшой сети: выбор подсети, маска, адрес сети и широковещательный адрес. Сдаётся таблица адресов и проверка связи между машинами.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">IP-адресация и маски</t>
+          <t xml:space="preserve">маска, адрес сети, широковещательный адрес, хост, двоичная запись</t>
         </is>
       </c>
     </row>
@@ -315,12 +315,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Стек TCP/IP»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Практический стек TCP/IP сжимает семь уровней OSI в четыре. Он же задаёт, где работают IP, TCP и прикладные протоколы.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стек TCP/IP</t>
+          <t xml:space="preserve">протокол, межсетевой уровень, транспорт, прикладной уровень, четыре уровня</t>
         </is>
       </c>
     </row>
@@ -345,16 +345,16 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Физический уровень и среды»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Физический уровень передаёт биты по среде: медь, оптика, радиоканал. От среды зависят скорость, дальность и помехоустойчивость.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Физический уровень и среды</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+          <t xml:space="preserve">витая пара, оптоволокно, затухание, помеха, пропускная способность</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">7-8</t>
@@ -375,12 +375,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Диагностика соединений; DNS и DHCP.</t>
+          <t xml:space="preserve">Две части: поиск неисправности по цепочке адрес, шлюз, DNS, и настройка DHCP с проверкой выдачи адресов. Сдаётся отчёт с командами и выводами.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Диагностика соединений, DNS и DHCP</t>
+          <t xml:space="preserve">шлюз, ipconfig, nslookup, аренда адреса, отчёт</t>
         </is>
       </c>
     </row>
@@ -405,16 +405,16 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Канальный уровень и Ethernet»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Канальный уровень собирает биты в кадры и передаёт их в пределах одной сети. Кадр Ethernet несёт MAC-адреса, тип и контрольную сумму.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Канальный уровень и Ethernet</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
+          <t xml:space="preserve">кадр, MAC-адрес, контрольная сумма, коммутатор, коллизия</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
@@ -435,12 +435,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «HTTP и HTTPS»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Запрос и ответ HTTP разбираются в браузере и Postman: методы, коды состояния, заголовки. Затем тот же запрос повторяется по HTTPS с проверкой сертификата.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP и HTTPS</t>
+          <t xml:space="preserve">запрос, код состояния, заголовок, сертификат, Postman</t>
         </is>
       </c>
     </row>
@@ -465,12 +465,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «MAC-адреса и коммутация»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Коммутатор учит таблицу MAC по входящим кадрам и пересылает кадр только в нужный порт. Так общая среда превращается в набор отдельных каналов.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAC-адреса и коммутация</t>
+          <t xml:space="preserve">таблица MAC, порт, широковещание, unicast, обучение коммутатора</t>
         </is>
       </c>
     </row>
@@ -495,16 +495,16 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Сетевой уровень и IP»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Сетевой уровень отвечает за доставку пакета между разными сетями. IP-адрес и маршрут задают, куда пакет пойдёт дальше.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сетевой уровень и IP</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
+          <t xml:space="preserve">пакет, маршрутизатор, IP-адрес, маршрут, TTL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">13-14</t>
@@ -525,12 +525,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Сетевые службы; Маршрутизация и VPN.</t>
+          <t xml:space="preserve">Две части: поднятие сетевой службы на виртуальной машине и настройка маршрута с туннелем. Сдаётся схема сети с адресами и отчёт о проверке доступа.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сетевые службы, Маршрутизация и VPN</t>
+          <t xml:space="preserve">служба, статический маршрут, туннель, шлюз, проверка доступа</t>
         </is>
       </c>
     </row>
@@ -555,16 +555,16 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «IPv4-адресация»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">IPv4-адрес состоит из 32 бит и делится маской на номер сети и номер узла. Классы, частные диапазоны и служебные адреса задают правила назначения.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">IPv4-адресация</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="45" customHeight="1">
+          <t xml:space="preserve">октет, маска, частный диапазон, узел, класс адреса</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
@@ -585,16 +585,16 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Мониторинг и безопасность»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Наблюдение за сетью на виртуальном стенде: снятие трафика, чтение журналов, проверка открытых портов. Сдаётся отчёт с найденными событиями и выводами.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мониторинг и безопасность</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
+          <t xml:space="preserve">журнал, соединение, открытый порт, событие, наблюдение</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
@@ -615,12 +615,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Подсети и маски»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Маска переменной длины делит сеть на подсети под отделы или сегменты. Расчёт показывает, сколько подсетей нужно и сколько адресов останется в каждой.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Подсети и маски</t>
+          <t xml:space="preserve">подсеть, префикс, VLSM, широковещание, диапазон адресов</t>
         </is>
       </c>
     </row>
@@ -645,16 +645,16 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Итоговая схема сети ИС»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Схема сети учебной информационной системы: сегменты, адресация, серверы и точки выхода. Сдаётся схема в draw.io с таблицей адресов и пояснениями.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Итоговая схема сети ИС</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
+          <t xml:space="preserve">сегмент, адресный план, сервер, точка выхода, условное обозначение</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
@@ -675,16 +675,16 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «IPv6»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">IPv6 расширяет адрес до 128 бит и убирает необходимость в NAT. Запись адреса короче за счёт сжатия нулевых групп.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">IPv6</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
+          <t xml:space="preserve">128 бит, шестнадцатеричная группа, сжатие нулей, link-local, префикс</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">20</t>
@@ -705,12 +705,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Маршрутизация»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Маршрутизатор выбирает путь по таблице: самый длинный совпавший префикс и метрика решают, куда отправить пакет. Статические и динамические маршруты дополняют друг друга.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Маршрутизация</t>
+          <t xml:space="preserve">таблица маршрутизации, префикс, метрика, шлюз по умолчанию, динамический маршрут</t>
         </is>
       </c>
     </row>
@@ -735,16 +735,16 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Транспортный уровень»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Транспортный уровень доставляет данные конкретному приложению и отвечает за надёжность. TCP и UDP решают эту задачу по-разному.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Транспортный уровень</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
+          <t xml:space="preserve">сегмент, мультиплексирование, надёжность, соединение, дейтаграмма</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">22</t>
@@ -765,16 +765,16 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «TCP»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">TCP устанавливает соединение тремя шагами, нумерует байты и подтверждает приём. Потеря пакета вызывает повторную передачу, а окно ограничивает поток.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">TCP</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
+          <t xml:space="preserve">рукопожатие, подтверждение, повторная передача, окно, таймер</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">23</t>
@@ -795,12 +795,12 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «UDP»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">UDP отправляет дейтаграмму без соединения и подтверждений. Выигрыш в задержке ценой возможных потерь подходит для голоса, видео и запросов DNS.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UDP</t>
+          <t xml:space="preserve">дейтаграмма, без соединения, потеря, задержка, накладные расходы</t>
         </is>
       </c>
     </row>
@@ -825,16 +825,16 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Порты и сокеты»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Порт указывает приложение внутри узла, а сокет связывает адрес, порт и протокол. Пара сокетов однозначно определяет соединение.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Порты и сокеты</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
+          <t xml:space="preserve">динамический диапазон, соединение, прослушивание, адрес узла, приложение</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">25</t>
@@ -855,16 +855,16 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «DNS»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">DNS переводит имя в адрес через цепочку серверов: кэш, корневой, доменный, авторитетный. Запись типа A, AAAA, MX или CNAME отвечает на свой вопрос.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
+          <t xml:space="preserve">имя, зона, кэш, тип записи, резолвер</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">26</t>
@@ -885,12 +885,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «DHCP»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">DHCP выдаёт адрес в четыре шага: обнаружение, предложение, запрос, подтверждение. Аренда ограничена сроком, а резервирование закрепляет адрес за устройством.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DHCP</t>
+          <t xml:space="preserve">аренда, предложение, подтверждение, пул адресов, резервирование</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «HTTP и HTTPS»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">HTTP работает по схеме запрос и ответ и не хранит состояние. HTTPS закрывает тот же обмен шифрованием TLS и подтверждает сервер сертификатом.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP и HTTPS</t>
+          <t xml:space="preserve">метод, код ответа, TLS, сертификат, сессия</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Электронная почта»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Письмо идёт от клиента к серверу отправки, затем к серверу получателя, где ждёт в ящике. SMTP передаёт, IMAP и POP3 забирают.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Электронная почта</t>
+          <t xml:space="preserve">SMTP, IMAP, POP3, ящик, заголовок письма</t>
         </is>
       </c>
     </row>
@@ -975,16 +975,16 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «FTP и файловые службы»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">FTP передаёт файлы по двум соединениям: командному и данным. SMB и сетевые папки дают общий доступ к файлам внутри локальной сети.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTP и файловые службы</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
+          <t xml:space="preserve">командное соединение, канал данных, пассивный режим, SMB, права доступа</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="45" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «VPN»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">VPN заворачивает пакет в новый пакет и проводит его через туннель между шлюзами. Данные защищены, а внешний адрес выглядит как адрес шлюза.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">VPN</t>
+          <t xml:space="preserve">туннель, инкапсуляция, шифрование, шлюз, удалённый доступ</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Беспроводные сети»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Wi-Fi делит общую радиосреду между клиентами: точка доступа согласует доступ и шифрует трафик. Каналы, диапазоны и помехи задают реальную скорость.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Беспроводные сети</t>
+          <t xml:space="preserve">точка доступа, SSID, канал, диапазон, шифрование</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Сетевые ОС и домены»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Домен объединяет компьютеры общим каталогом пользователей и политик. Контроллер домена проверяет вход, а групповые политики задают настройки.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сетевые ОС и домены</t>
+          <t xml:space="preserve">рабочая группа, контроллер, каталог пользователей, группа безопасности, политика</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Виртуализация сетей»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Виртуальные коммутаторы и сети связывают машины внутри гипервизора. Режимы NAT, мост и внутренняя сеть задают, что видно снаружи.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Виртуализация сетей</t>
+          <t xml:space="preserve">гипервизор, виртуальный коммутатор, мост, NAT, стенд</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Сетевые службы в ИС»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Информационная система опирается на набор служб: веб-сервер, база данных, каталог, файловый сервер. Их размещение и связи задают схему сети ИС.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сетевые службы в ИС</t>
+          <t xml:space="preserve">веб-сервер, СУБД, каталог, файловый сервер, размещение</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Диагностика сети»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Неисправность ищут по цепочке от кабеля к приложению: адрес, шлюз, DNS, порт службы. Каждый шаг отсекает часть возможных причин.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Диагностика сети</t>
+          <t xml:space="preserve">ping, tracert, nslookup, netstat, причина</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Мониторинг сети»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Мониторинг собирает показатели узлов и каналов: загрузку, потери, задержку, доступность. Порог и оповещение превращают цифры в реакцию.</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мониторинг сети</t>
+          <t xml:space="preserve">показатель, порог, оповещение, загрузка, доступность</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Безопасность сетей»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Угрозы сети идут от перехвата трафика до подмены узла. Защита строится слоями: сегментация, шифрование, фильтрация и парольная политика.</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Безопасность сетей</t>
+          <t xml:space="preserve">угроза, сегментация, фильтрация, шифрование, парольная политика</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Проектирование сети ИС»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Проект сети ИС начинается с требований: число узлов, службы, нагрузка, безопасность. Дальше идут адресный план, схема сегментов и план проверки.</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проектирование сети ИС</t>
+          <t xml:space="preserve">требование, адресный план, сегмент, нагрузка, план проверки</t>
         </is>
       </c>
     </row>

--- a/courses/2/networks/dist/Учебный_план_Компьютерные_сети.xlsx
+++ b/courses/2/networks/dist/Учебный_план_Компьютерные_сети.xlsx
@@ -160,7 +160,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Минуты</t>
+          <t xml:space="preserve">Часы</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="D6" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -221,7 +221,7 @@
         </is>
       </c>
       <c r="D7" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -251,7 +251,7 @@
         </is>
       </c>
       <c r="D8" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
         </is>
       </c>
       <c r="D9" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -311,7 +311,7 @@
         </is>
       </c>
       <c r="D10" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="D11" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -371,7 +371,7 @@
         </is>
       </c>
       <c r="D12" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="D13" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -431,7 +431,7 @@
         </is>
       </c>
       <c r="D14" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="D16" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D17" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="D18" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D19" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D20" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="D21" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D22" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D23" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="D24" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="D25" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D26" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="D27" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D28" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="D29" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D31" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="D32" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="D33" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="D34" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="D35" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D36" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D37" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D38" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="D39" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="D40" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="D41" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="D42" s="6">
-        <v>3420</v>
+        <v>76</v>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>

--- a/courses/2/networks/dist/Учебный_план_Компьютерные_сети.xlsx
+++ b/courses/2/networks/dist/Учебный_план_Компьютерные_сети.xlsx
@@ -204,7 +204,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="45" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
@@ -212,12 +212,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 1. Настройка сети в VirtualBox</t>
+          <t xml:space="preserve">Лекция 2. Модель OSI</t>
         </is>
       </c>
       <c r="D7" s="6">
@@ -225,12 +225,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Две виртуальные машины соединяются в сеть внутри VirtualBox: режим адаптера, адреса, проверка связи. Сдаётся отчёт со схемой и выводом команд проверки.</t>
+          <t xml:space="preserve">Семь уровней OSI делят задачу передачи на слои: от кабеля до приложения. Каждый уровень добавляет свой заголовок и работает с данными по-своему.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">виртуальная машина, адаптер, NAT, ping, хост</t>
+          <t xml:space="preserve">уровень, инкапсуляция, заголовок, прикладной уровень, канальный уровень</t>
         </is>
       </c>
     </row>
@@ -247,7 +247,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 2. Модель OSI</t>
+          <t xml:space="preserve">Лекция 3. Стек TCP/IP</t>
         </is>
       </c>
       <c r="D8" s="6">
@@ -255,16 +255,16 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Семь уровней OSI делят задачу передачи на слои: от кабеля до приложения. Каждый уровень добавляет свой заголовок и работает с данными по-своему.</t>
+          <t xml:space="preserve">Практический стек TCP/IP сжимает семь уровней OSI в четыре. Он же задаёт, где работают IP, TCP и прикладные протоколы.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">уровень, инкапсуляция, заголовок, прикладной уровень, канальный уровень</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t xml:space="preserve">протокол, межсетевой уровень, транспорт, прикладной уровень, четыре уровня</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
@@ -272,12 +272,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 2. IP-адресация и маски</t>
+          <t xml:space="preserve">Лекция 4. Физический уровень и среды</t>
         </is>
       </c>
       <c r="D9" s="6">
@@ -285,12 +285,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Расчёт адресов для небольшой сети: выбор подсети, маска, адрес сети и широковещательный адрес. Сдаётся таблица адресов и проверка связи между машинами.</t>
+          <t xml:space="preserve">Физический уровень передаёт биты по среде: медь, оптика, радиоканал. От среды зависят скорость, дальность и помехоустойчивость.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">маска, адрес сети, широковещательный адрес, хост, двоичная запись</t>
+          <t xml:space="preserve">витая пара, оптоволокно, затухание, помеха, пропускная способность</t>
         </is>
       </c>
     </row>
@@ -307,7 +307,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 3. Стек TCP/IP</t>
+          <t xml:space="preserve">Лекция 5. Канальный уровень и Ethernet</t>
         </is>
       </c>
       <c r="D10" s="6">
@@ -315,12 +315,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практический стек TCP/IP сжимает семь уровней OSI в четыре. Он же задаёт, где работают IP, TCP и прикладные протоколы.</t>
+          <t xml:space="preserve">Канальный уровень собирает биты в кадры и передаёт их в пределах одной сети. Кадр Ethernet несёт MAC-адреса, тип и контрольную сумму.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">протокол, межсетевой уровень, транспорт, прикладной уровень, четыре уровня</t>
+          <t xml:space="preserve">кадр, MAC-адрес, контрольная сумма, коммутатор, коллизия</t>
         </is>
       </c>
     </row>
@@ -337,7 +337,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 4. Физический уровень и среды</t>
+          <t xml:space="preserve">Лекция 6. MAC-адреса и коммутация</t>
         </is>
       </c>
       <c r="D11" s="6">
@@ -345,49 +345,49 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Физический уровень передаёт биты по среде: медь, оптика, радиоканал. От среды зависят скорость, дальность и помехоустойчивость.</t>
+          <t xml:space="preserve">Коммутатор учит таблицу MAC по входящим кадрам и пересылает кадр только в нужный порт. Так общая среда превращается в набор отдельных каналов.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">витая пара, оптоволокно, затухание, помеха, пропускная способность</t>
+          <t xml:space="preserve">таблица MAC, порт, широковещание, unicast, обучение коммутатора</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 3. Диагностика соединений; DNS и DHCP</t>
+          <t xml:space="preserve">Лекция 7. Сетевой уровень и IP</t>
         </is>
       </c>
       <c r="D12" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Две части: поиск неисправности по цепочке адрес, шлюз, DNS, и настройка DHCP с проверкой выдачи адресов. Сдаётся отчёт с командами и выводами.</t>
+          <t xml:space="preserve">Сетевой уровень отвечает за доставку пакета между разными сетями. IP-адрес и маршрут задают, куда пакет пойдёт дальше.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">шлюз, ipconfig, nslookup, аренда адреса, отчёт</t>
+          <t xml:space="preserve">пакет, маршрутизатор, IP-адрес, маршрут, TTL</t>
         </is>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -397,7 +397,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 5. Канальный уровень и Ethernet</t>
+          <t xml:space="preserve">Лекция 8. IPv4-адресация</t>
         </is>
       </c>
       <c r="D13" s="6">
@@ -405,59 +405,59 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Канальный уровень собирает биты в кадры и передаёт их в пределах одной сети. Кадр Ethernet несёт MAC-адреса, тип и контрольную сумму.</t>
+          <t xml:space="preserve">IPv4-адрес состоит из 32 бит и делится маской на номер сети и номер узла. Классы, частные диапазоны и служебные адреса задают правила назначения.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">кадр, MAC-адрес, контрольная сумма, коммутатор, коллизия</t>
+          <t xml:space="preserve">октет, маска, частный диапазон, узел, класс адреса</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 9. Подсети и маски</t>
+        </is>
+      </c>
+      <c r="D14" s="6">
+        <v>2</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Маска переменной длины делит сеть на подсети под отделы или сегменты. Расчёт показывает, сколько подсетей нужно и сколько адресов останется в каждой.</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">подсеть, префикс, VLSM, широковещание, диапазон адресов</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Практика</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика 4. HTTP и HTTPS</t>
-        </is>
-      </c>
-      <c r="D14" s="6">
-        <v>2</v>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Запрос и ответ HTTP разбираются в браузере и Postman: методы, коды состояния, заголовки. Затем тот же запрос повторяется по HTTPS с проверкой сертификата.</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">запрос, код состояния, заголовок, сертификат, Postman</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 6. MAC-адреса и коммутация</t>
+          <t xml:space="preserve">Практика 1. IP-адресация и маски</t>
         </is>
       </c>
       <c r="D15" s="6">
@@ -465,79 +465,79 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Коммутатор учит таблицу MAC по входящим кадрам и пересылает кадр только в нужный порт. Так общая среда превращается в набор отдельных каналов.</t>
+          <t xml:space="preserve">Расчёт адресов для небольшой сети: выбор подсети, маска, адрес сети и широковещательный адрес. Сдаётся таблица адресов и проверка связи между машинами.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">таблица MAC, порт, широковещание, unicast, обучение коммутатора</t>
+          <t xml:space="preserve">маска, адрес сети, широковещательный адрес, хост, двоичная запись</t>
         </is>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 10. IPv6</t>
+        </is>
+      </c>
+      <c r="D16" s="6">
+        <v>2</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IPv6 расширяет адрес до 128 бит и убирает необходимость в NAT. Запись адреса короче за счёт сжатия нулевых групп.</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128 бит, шестнадцатеричная группа, сжатие нулей, link-local, префикс</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 7. Сетевой уровень и IP</t>
-        </is>
-      </c>
-      <c r="D16" s="6">
-        <v>2</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Сетевой уровень отвечает за доставку пакета между разными сетями. IP-адрес и маршрут задают, куда пакет пойдёт дальше.</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">пакет, маршрутизатор, IP-адрес, маршрут, TTL</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13-14</t>
-        </is>
-      </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 5. Сетевые службы; Маршрутизация и VPN</t>
+          <t xml:space="preserve">Лекция 11. Маршрутизация</t>
         </is>
       </c>
       <c r="D17" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Две части: поднятие сетевой службы на виртуальной машине и настройка маршрута с туннелем. Сдаётся схема сети с адресами и отчёт о проверке доступа.</t>
+          <t xml:space="preserve">Маршрутизатор выбирает путь по таблице: самый длинный совпавший префикс и метрика решают, куда отправить пакет. Статические и динамические маршруты дополняют друг друга.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">служба, статический маршрут, туннель, шлюз, проверка доступа</t>
+          <t xml:space="preserve">таблица маршрутизации, префикс, метрика, шлюз по умолчанию, динамический маршрут</t>
         </is>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 8. IPv4-адресация</t>
+          <t xml:space="preserve">Лекция 12. Транспортный уровень</t>
         </is>
       </c>
       <c r="D18" s="6">
@@ -555,29 +555,29 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">IPv4-адрес состоит из 32 бит и делится маской на номер сети и номер узла. Классы, частные диапазоны и служебные адреса задают правила назначения.</t>
+          <t xml:space="preserve">Транспортный уровень доставляет данные конкретному приложению и отвечает за надёжность. TCP и UDP решают эту задачу по-разному.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">октет, маска, частный диапазон, узел, класс адреса</t>
+          <t xml:space="preserve">сегмент, мультиплексирование, надёжность, соединение, дейтаграмма</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 6. Мониторинг и безопасность</t>
+          <t xml:space="preserve">Лекция 13. TCP</t>
         </is>
       </c>
       <c r="D19" s="6">
@@ -585,19 +585,19 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наблюдение за сетью на виртуальном стенде: снятие трафика, чтение журналов, проверка открытых портов. Сдаётся отчёт с найденными событиями и выводами.</t>
+          <t xml:space="preserve">TCP устанавливает соединение тремя шагами, нумерует байты и подтверждает приём. Потеря пакета вызывает повторную передачу, а окно ограничивает поток.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">журнал, соединение, открытый порт, событие, наблюдение</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1">
+          <t xml:space="preserve">рукопожатие, подтверждение, повторная передача, окно, таймер</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 9. Подсети и маски</t>
+          <t xml:space="preserve">Лекция 14. UDP</t>
         </is>
       </c>
       <c r="D20" s="6">
@@ -615,29 +615,29 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Маска переменной длины делит сеть на подсети под отделы или сегменты. Расчёт показывает, сколько подсетей нужно и сколько адресов останется в каждой.</t>
+          <t xml:space="preserve">UDP отправляет дейтаграмму без соединения и подтверждений. Выигрыш в задержке ценой возможных потерь подходит для голоса, видео и запросов DNS.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">подсеть, префикс, VLSM, широковещание, диапазон адресов</t>
+          <t xml:space="preserve">дейтаграмма, без соединения, потеря, задержка, накладные расходы</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 7. Итоговая схема сети ИС</t>
+          <t xml:space="preserve">Лекция 15. Порты и сокеты</t>
         </is>
       </c>
       <c r="D21" s="6">
@@ -645,19 +645,19 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Схема сети учебной информационной системы: сегменты, адресация, серверы и точки выхода. Сдаётся схема в draw.io с таблицей адресов и пояснениями.</t>
+          <t xml:space="preserve">Порт указывает приложение внутри узла, а сокет связывает адрес, порт и протокол. Пара сокетов однозначно определяет соединение.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">сегмент, адресный план, сервер, точка выхода, условное обозначение</t>
+          <t xml:space="preserve">динамический диапазон, соединение, прослушивание, адрес узла, приложение</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 10. IPv6</t>
+          <t xml:space="preserve">Лекция 16. DNS</t>
         </is>
       </c>
       <c r="D22" s="6">
@@ -675,19 +675,19 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">IPv6 расширяет адрес до 128 бит и убирает необходимость в NAT. Запись адреса короче за счёт сжатия нулевых групп.</t>
+          <t xml:space="preserve">DNS переводит имя в адрес через цепочку серверов: кэш, корневой, доменный, авторитетный. Запись типа A, AAAA, MX или CNAME отвечает на свой вопрос.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">128 бит, шестнадцатеричная группа, сжатие нулей, link-local, префикс</t>
+          <t xml:space="preserve">имя, зона, кэш, тип записи, резолвер</t>
         </is>
       </c>
     </row>
     <row r="23" ht="60" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 11. Маршрутизация</t>
+          <t xml:space="preserve">Лекция 17. DHCP</t>
         </is>
       </c>
       <c r="D23" s="6">
@@ -705,19 +705,19 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Маршрутизатор выбирает путь по таблице: самый длинный совпавший префикс и метрика решают, куда отправить пакет. Статические и динамические маршруты дополняют друг друга.</t>
+          <t xml:space="preserve">DHCP выдаёт адрес в четыре шага: обнаружение, предложение, запрос, подтверждение. Аренда ограничена сроком, а резервирование закрепляет адрес за устройством.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">таблица маршрутизации, префикс, метрика, шлюз по умолчанию, динамический маршрут</t>
+          <t xml:space="preserve">аренда, предложение, подтверждение, пул адресов, резервирование</t>
         </is>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 12. Транспортный уровень</t>
+          <t xml:space="preserve">Лекция 18. HTTP и HTTPS</t>
         </is>
       </c>
       <c r="D24" s="6">
@@ -735,29 +735,29 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Транспортный уровень доставляет данные конкретному приложению и отвечает за надёжность. TCP и UDP решают эту задачу по-разному.</t>
+          <t xml:space="preserve">HTTP работает по схеме запрос и ответ и не хранит состояние. HTTPS закрывает тот же обмен шифрованием TLS и подтверждает сервер сертификатом.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">сегмент, мультиплексирование, надёжность, соединение, дейтаграмма</t>
+          <t xml:space="preserve">метод, код ответа, TLS, сертификат, сессия</t>
         </is>
       </c>
     </row>
     <row r="25" ht="60" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 13. TCP</t>
+          <t xml:space="preserve">Практика 2. HTTP и HTTPS</t>
         </is>
       </c>
       <c r="D25" s="6">
@@ -765,19 +765,19 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">TCP устанавливает соединение тремя шагами, нумерует байты и подтверждает приём. Потеря пакета вызывает повторную передачу, а окно ограничивает поток.</t>
+          <t xml:space="preserve">Запрос и ответ HTTP разбираются в браузере и Postman: методы, коды состояния, заголовки. Затем тот же запрос повторяется по HTTPS с проверкой сертификата.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">рукопожатие, подтверждение, повторная передача, окно, таймер</t>
+          <t xml:space="preserve">запрос, код состояния, заголовок, сертификат, Postman</t>
         </is>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 14. UDP</t>
+          <t xml:space="preserve">Лекция 19. Электронная почта</t>
         </is>
       </c>
       <c r="D26" s="6">
@@ -795,19 +795,19 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UDP отправляет дейтаграмму без соединения и подтверждений. Выигрыш в задержке ценой возможных потерь подходит для голоса, видео и запросов DNS.</t>
+          <t xml:space="preserve">Письмо идёт от клиента к серверу отправки, затем к серверу получателя, где ждёт в ящике. SMTP передаёт, IMAP и POP3 забирают.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">дейтаграмма, без соединения, потеря, задержка, накладные расходы</t>
+          <t xml:space="preserve">SMTP, IMAP, POP3, ящик, заголовок письма</t>
         </is>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 15. Порты и сокеты</t>
+          <t xml:space="preserve">Лекция 20. FTP и файловые службы</t>
         </is>
       </c>
       <c r="D27" s="6">
@@ -825,19 +825,19 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Порт указывает приложение внутри узла, а сокет связывает адрес, порт и протокол. Пара сокетов однозначно определяет соединение.</t>
+          <t xml:space="preserve">FTP передаёт файлы по двум соединениям: командному и данным. SMB и сетевые папки дают общий доступ к файлам внутри локальной сети.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">динамический диапазон, соединение, прослушивание, адрес узла, приложение</t>
+          <t xml:space="preserve">командное соединение, канал данных, пассивный режим, SMB, права доступа</t>
         </is>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 16. DNS</t>
+          <t xml:space="preserve">Лекция 21. VPN</t>
         </is>
       </c>
       <c r="D28" s="6">
@@ -855,19 +855,19 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNS переводит имя в адрес через цепочку серверов: кэш, корневой, доменный, авторитетный. Запись типа A, AAAA, MX или CNAME отвечает на свой вопрос.</t>
+          <t xml:space="preserve">VPN заворачивает пакет в новый пакет и проводит его через туннель между шлюзами. Данные защищены, а внешний адрес выглядит как адрес шлюза.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">имя, зона, кэш, тип записи, резолвер</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="60" customHeight="1">
+          <t xml:space="preserve">туннель, инкапсуляция, шифрование, шлюз, удалённый доступ</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 17. DHCP</t>
+          <t xml:space="preserve">Лекция 22. Беспроводные сети</t>
         </is>
       </c>
       <c r="D29" s="6">
@@ -885,19 +885,19 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DHCP выдаёт адрес в четыре шага: обнаружение, предложение, запрос, подтверждение. Аренда ограничена сроком, а резервирование закрепляет адрес за устройством.</t>
+          <t xml:space="preserve">Wi-Fi делит общую радиосреду между клиентами: точка доступа согласует доступ и шифрует трафик. Каналы, диапазоны и помехи задают реальную скорость.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">аренда, предложение, подтверждение, пул адресов, резервирование</t>
+          <t xml:space="preserve">точка доступа, SSID, канал, диапазон, шифрование</t>
         </is>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 18. HTTP и HTTPS</t>
+          <t xml:space="preserve">Лекция 23. Сетевые ОС и домены</t>
         </is>
       </c>
       <c r="D30" s="6">
@@ -915,19 +915,19 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP работает по схеме запрос и ответ и не хранит состояние. HTTPS закрывает тот же обмен шифрованием TLS и подтверждает сервер сертификатом.</t>
+          <t xml:space="preserve">Домен объединяет компьютеры общим каталогом пользователей и политик. Контроллер домена проверяет вход, а групповые политики задают настройки.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">метод, код ответа, TLS, сертификат, сессия</t>
+          <t xml:space="preserve">рабочая группа, контроллер, каталог пользователей, группа безопасности, политика</t>
         </is>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 19. Электронная почта</t>
+          <t xml:space="preserve">Лекция 24. Виртуализация сетей</t>
         </is>
       </c>
       <c r="D31" s="6">
@@ -945,29 +945,29 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Письмо идёт от клиента к серверу отправки, затем к серверу получателя, где ждёт в ящике. SMTP передаёт, IMAP и POP3 забирают.</t>
+          <t xml:space="preserve">Виртуальные коммутаторы и сети связывают машины внутри гипервизора. Режимы NAT, мост и внутренняя сеть задают, что видно снаружи.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SMTP, IMAP, POP3, ящик, заголовок письма</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="45" customHeight="1">
+          <t xml:space="preserve">гипервизор, виртуальный коммутатор, мост, NAT, стенд</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 20. FTP и файловые службы</t>
+          <t xml:space="preserve">Практика 3. Настройка сети в VirtualBox</t>
         </is>
       </c>
       <c r="D32" s="6">
@@ -975,19 +975,19 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTP передаёт файлы по двум соединениям: командному и данным. SMB и сетевые папки дают общий доступ к файлам внутри локальной сети.</t>
+          <t xml:space="preserve">Две виртуальные машины соединяются в сеть внутри VirtualBox: режим адаптера, адреса, проверка связи. Сдаётся отчёт со схемой и выводом команд проверки.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">командное соединение, канал данных, пассивный режим, SMB, права доступа</t>
+          <t xml:space="preserve">виртуальная машина, адаптер, NAT, ping, хост</t>
         </is>
       </c>
     </row>
     <row r="33" ht="45" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 21. VPN</t>
+          <t xml:space="preserve">Лекция 25. Сетевые службы в ИС</t>
         </is>
       </c>
       <c r="D33" s="6">
@@ -1005,49 +1005,49 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">VPN заворачивает пакет в новый пакет и проводит его через туннель между шлюзами. Данные защищены, а внешний адрес выглядит как адрес шлюза.</t>
+          <t xml:space="preserve">Информационная система опирается на набор служб: веб-сервер, база данных, каталог, файловый сервер. Их размещение и связи задают схему сети ИС.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">туннель, инкапсуляция, шифрование, шлюз, удалённый доступ</t>
+          <t xml:space="preserve">веб-сервер, СУБД, каталог, файловый сервер, размещение</t>
         </is>
       </c>
     </row>
     <row r="34" ht="45" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">29-30</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 22. Беспроводные сети</t>
+          <t xml:space="preserve">Практика 4. Сетевые службы; Маршрутизация и VPN</t>
         </is>
       </c>
       <c r="D34" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wi-Fi делит общую радиосреду между клиентами: точка доступа согласует доступ и шифрует трафик. Каналы, диапазоны и помехи задают реальную скорость.</t>
+          <t xml:space="preserve">Две части: поднятие сетевой службы на виртуальной машине и настройка маршрута с туннелем. Сдаётся схема сети с адресами и отчёт о проверке доступа.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">точка доступа, SSID, канал, диапазон, шифрование</t>
+          <t xml:space="preserve">служба, статический маршрут, туннель, шлюз, проверка доступа</t>
         </is>
       </c>
     </row>
     <row r="35" ht="45" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 23. Сетевые ОС и домены</t>
+          <t xml:space="preserve">Лекция 26. Диагностика сети</t>
         </is>
       </c>
       <c r="D35" s="6">
@@ -1065,42 +1065,42 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Домен объединяет компьютеры общим каталогом пользователей и политик. Контроллер домена проверяет вход, а групповые политики задают настройки.</t>
+          <t xml:space="preserve">Неисправность ищут по цепочке от кабеля к приложению: адрес, шлюз, DNS, порт службы. Каждый шаг отсекает часть возможных причин.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">рабочая группа, контроллер, каталог пользователей, группа безопасности, политика</t>
+          <t xml:space="preserve">ping, tracert, nslookup, netstat, причина</t>
         </is>
       </c>
     </row>
     <row r="36" ht="45" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32-33</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 24. Виртуализация сетей</t>
+          <t xml:space="preserve">Практика 5. Диагностика соединений; DNS и DHCP</t>
         </is>
       </c>
       <c r="D36" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Виртуальные коммутаторы и сети связывают машины внутри гипервизора. Режимы NAT, мост и внутренняя сеть задают, что видно снаружи.</t>
+          <t xml:space="preserve">Две части: поиск неисправности по цепочке адрес, шлюз, DNS, и настройка DHCP с проверкой выдачи адресов. Сдаётся отчёт с командами и выводами.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">гипервизор, виртуальный коммутатор, мост, NAT, стенд</t>
+          <t xml:space="preserve">шлюз, ipconfig, nslookup, аренда адреса, отчёт</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 25. Сетевые службы в ИС</t>
+          <t xml:space="preserve">Лекция 27. Мониторинг сети</t>
         </is>
       </c>
       <c r="D37" s="6">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Информационная система опирается на набор служб: веб-сервер, база данных, каталог, файловый сервер. Их размещение и связи задают схему сети ИС.</t>
+          <t xml:space="preserve">Мониторинг собирает показатели узлов и каналов: загрузку, потери, задержку, доступность. Порог и оповещение превращают цифры в реакцию.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">веб-сервер, СУБД, каталог, файловый сервер, размещение</t>
+          <t xml:space="preserve">показатель, порог, оповещение, загрузка, доступность</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 26. Диагностика сети</t>
+          <t xml:space="preserve">Лекция 28. Безопасность сетей</t>
         </is>
       </c>
       <c r="D38" s="6">
@@ -1155,16 +1155,16 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Неисправность ищут по цепочке от кабеля к приложению: адрес, шлюз, DNS, порт службы. Каждый шаг отсекает часть возможных причин.</t>
+          <t xml:space="preserve">Угрозы сети идут от перехвата трафика до подмены узла. Защита строится слоями: сегментация, шифрование, фильтрация и парольная политика.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ping, tracert, nslookup, netstat, причина</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="45" customHeight="1">
+          <t xml:space="preserve">угроза, сегментация, фильтрация, шифрование, парольная политика</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">36</t>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 27. Мониторинг сети</t>
+          <t xml:space="preserve">Практика 6. Мониторинг и безопасность</t>
         </is>
       </c>
       <c r="D39" s="6">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мониторинг собирает показатели узлов и каналов: загрузку, потери, задержку, доступность. Порог и оповещение превращают цифры в реакцию.</t>
+          <t xml:space="preserve">Наблюдение за сетью на виртуальном стенде: снятие трафика, чтение журналов, проверка открытых портов. Сдаётся отчёт с найденными событиями и выводами.</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">показатель, порог, оповещение, загрузка, доступность</t>
+          <t xml:space="preserve">журнал, соединение, открытый порт, событие, наблюдение</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 28. Безопасность сетей</t>
+          <t xml:space="preserve">Лекция 29. Проектирование сети ИС</t>
         </is>
       </c>
       <c r="D40" s="6">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Угрозы сети идут от перехвата трафика до подмены узла. Защита строится слоями: сегментация, шифрование, фильтрация и парольная политика.</t>
+          <t xml:space="preserve">Проект сети ИС начинается с требований: число узлов, службы, нагрузка, безопасность. Дальше идут адресный план, схема сегментов и план проверки.</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">угроза, сегментация, фильтрация, шифрование, парольная политика</t>
+          <t xml:space="preserve">требование, адресный план, сегмент, нагрузка, план проверки</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 29. Проектирование сети ИС</t>
+          <t xml:space="preserve">Практика 7. Итоговая схема сети ИС</t>
         </is>
       </c>
       <c r="D41" s="6">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проект сети ИС начинается с требований: число узлов, службы, нагрузка, безопасность. Дальше идут адресный план, схема сегментов и план проверки.</t>
+          <t xml:space="preserve">Схема сети учебной информационной системы: сегменты, адресация, серверы и точки выхода. Сдаётся схема в draw.io с таблицей адресов и пояснениями.</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">требование, адресный план, сегмент, нагрузка, план проверки</t>
+          <t xml:space="preserve">сегмент, адресный план, сервер, точка выхода, условное обозначение</t>
         </is>
       </c>
     </row>
